--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93370</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93372</v>
+        <v>93387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93388</v>
+        <v>93389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28219-2026 artfynd.xlsx
+++ b/artfynd/A 28219-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135706026</v>
       </c>
       <c r="B2" t="n">
-        <v>93397</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
